--- a/research/traditional_assets/database/data/vietnam/vietnam_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.109</v>
+        <v>0.13</v>
       </c>
       <c r="E2">
-        <v>0.098</v>
+        <v>0.0323</v>
       </c>
       <c r="G2">
-        <v>0.1764705882352941</v>
+        <v>0.2551282051282051</v>
       </c>
       <c r="H2">
-        <v>0.1764705882352941</v>
+        <v>0.2551282051282051</v>
       </c>
       <c r="I2">
-        <v>0.2194570135746606</v>
+        <v>0.2166666666666666</v>
       </c>
       <c r="J2">
-        <v>0.1804683739289496</v>
+        <v>0.1763353413654619</v>
       </c>
       <c r="K2">
-        <v>15.5</v>
+        <v>13.6</v>
       </c>
       <c r="L2">
-        <v>0.1753393665158371</v>
+        <v>0.1743589743589744</v>
       </c>
       <c r="M2">
-        <v>8.529999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="N2">
-        <v>0.040832934418382</v>
+        <v>0.06704270749395649</v>
       </c>
       <c r="O2">
-        <v>0.5503225806451613</v>
+        <v>0.611764705882353</v>
       </c>
       <c r="P2">
-        <v>8.529999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="Q2">
-        <v>0.040832934418382</v>
+        <v>0.06704270749395649</v>
       </c>
       <c r="R2">
-        <v>0.5503225806451613</v>
+        <v>0.611764705882353</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>5.65</v>
+        <v>3.65</v>
       </c>
       <c r="V2">
-        <v>0.02704643370033509</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="W2">
-        <v>0.1183206106870229</v>
+        <v>0.09742120343839542</v>
       </c>
       <c r="X2">
-        <v>0.1240469833600718</v>
+        <v>0.1602898470840112</v>
       </c>
       <c r="Y2">
-        <v>-0.005726372673048943</v>
+        <v>-0.06286864364561581</v>
       </c>
       <c r="Z2">
-        <v>0.7155577141006961</v>
+        <v>0.5823068309070549</v>
       </c>
       <c r="AA2">
-        <v>0.1291355371160689</v>
+        <v>0.1026812738074358</v>
       </c>
       <c r="AB2">
-        <v>0.1240469833600718</v>
+        <v>0.1602898470840112</v>
       </c>
       <c r="AC2">
-        <v>0.005088553755997025</v>
+        <v>-0.05760857327657543</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-5.65</v>
+        <v>-3.65</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,28 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.02779827798277983</v>
+        <v>-0.0303030303030303</v>
       </c>
       <c r="AK2">
-        <v>-0.04174362763206502</v>
+        <v>-0.02682837192208747</v>
       </c>
       <c r="AL2">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>1.89</v>
+        <v>-0.418</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
-      <c r="AO2">
-        <v>10.26455026455026</v>
-      </c>
       <c r="AP2">
-        <v>-0.288265306122449</v>
+        <v>-0.2147058823529412</v>
       </c>
       <c r="AQ2">
-        <v>10.26455026455026</v>
+        <v>-40.43062200956938</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.109</v>
+        <v>0.13</v>
       </c>
       <c r="E3">
-        <v>0.098</v>
+        <v>0.0323</v>
       </c>
       <c r="G3">
-        <v>0.1764705882352941</v>
+        <v>0.2551282051282051</v>
       </c>
       <c r="H3">
-        <v>0.1764705882352941</v>
+        <v>0.2551282051282051</v>
       </c>
       <c r="I3">
-        <v>0.2194570135746606</v>
+        <v>0.2166666666666666</v>
       </c>
       <c r="J3">
-        <v>0.1804683739289496</v>
+        <v>0.1763353413654619</v>
       </c>
       <c r="K3">
-        <v>15.5</v>
+        <v>13.6</v>
       </c>
       <c r="L3">
-        <v>0.1753393665158371</v>
+        <v>0.1743589743589744</v>
       </c>
       <c r="M3">
-        <v>8.529999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="N3">
-        <v>0.040832934418382</v>
+        <v>0.06704270749395649</v>
       </c>
       <c r="O3">
-        <v>0.5503225806451613</v>
+        <v>0.611764705882353</v>
       </c>
       <c r="P3">
-        <v>8.529999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="Q3">
-        <v>0.040832934418382</v>
+        <v>0.06704270749395649</v>
       </c>
       <c r="R3">
-        <v>0.5503225806451613</v>
+        <v>0.611764705882353</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>5.65</v>
+        <v>3.65</v>
       </c>
       <c r="V3">
-        <v>0.02704643370033509</v>
+        <v>0.02941176470588235</v>
       </c>
       <c r="W3">
-        <v>0.1183206106870229</v>
+        <v>0.09742120343839542</v>
       </c>
       <c r="X3">
-        <v>0.1240469833600718</v>
+        <v>0.1602898470840112</v>
       </c>
       <c r="Y3">
-        <v>-0.005726372673048943</v>
+        <v>-0.06286864364561581</v>
       </c>
       <c r="Z3">
-        <v>0.7155577141006961</v>
+        <v>0.5823068309070549</v>
       </c>
       <c r="AA3">
-        <v>0.1291355371160689</v>
+        <v>0.1026812738074358</v>
       </c>
       <c r="AB3">
-        <v>0.1240469833600718</v>
+        <v>0.1602898470840112</v>
       </c>
       <c r="AC3">
-        <v>0.005088553755997025</v>
+        <v>-0.05760857327657543</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-5.65</v>
+        <v>-3.65</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,28 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.02779827798277983</v>
+        <v>-0.0303030303030303</v>
       </c>
       <c r="AK3">
-        <v>-0.04174362763206502</v>
+        <v>-0.02682837192208747</v>
       </c>
       <c r="AL3">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>1.89</v>
+        <v>-0.418</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
-      <c r="AO3">
-        <v>10.26455026455026</v>
-      </c>
       <c r="AP3">
-        <v>-0.288265306122449</v>
+        <v>-0.2147058823529412</v>
       </c>
       <c r="AQ3">
-        <v>10.26455026455026</v>
+        <v>-40.43062200956938</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/vietnam/vietnam_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/vietnam/vietnam_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.13</v>
+        <v>0.127</v>
       </c>
       <c r="E2">
-        <v>0.0323</v>
+        <v>0.133</v>
       </c>
       <c r="G2">
-        <v>0.2551282051282051</v>
+        <v>0.2115812917594655</v>
       </c>
       <c r="H2">
-        <v>0.2551282051282051</v>
+        <v>0.2115812917594655</v>
       </c>
       <c r="I2">
-        <v>0.2166666666666666</v>
+        <v>0.2494432071269488</v>
       </c>
       <c r="J2">
-        <v>0.1763353413654619</v>
+        <v>0.2105382789371901</v>
       </c>
       <c r="K2">
-        <v>13.6</v>
+        <v>20.4</v>
       </c>
       <c r="L2">
-        <v>0.1743589743589744</v>
+        <v>0.2271714922048998</v>
       </c>
       <c r="M2">
-        <v>8.32</v>
+        <v>6.19</v>
       </c>
       <c r="N2">
-        <v>0.06704270749395649</v>
+        <v>0.04045751633986928</v>
       </c>
       <c r="O2">
-        <v>0.611764705882353</v>
+        <v>0.3034313725490196</v>
       </c>
       <c r="P2">
-        <v>8.32</v>
+        <v>6.19</v>
       </c>
       <c r="Q2">
-        <v>0.06704270749395649</v>
+        <v>0.04045751633986928</v>
       </c>
       <c r="R2">
-        <v>0.611764705882353</v>
+        <v>0.3034313725490196</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,31 +636,31 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.65</v>
+        <v>3.51</v>
       </c>
       <c r="V2">
-        <v>0.02941176470588235</v>
+        <v>0.02294117647058823</v>
       </c>
       <c r="W2">
-        <v>0.09742120343839542</v>
+        <v>0.1473988439306358</v>
       </c>
       <c r="X2">
-        <v>0.1602898470840112</v>
+        <v>0.1351511861324736</v>
       </c>
       <c r="Y2">
-        <v>-0.06286864364561581</v>
+        <v>0.0122476577981622</v>
       </c>
       <c r="Z2">
-        <v>0.5823068309070549</v>
+        <v>0.6664192949907235</v>
       </c>
       <c r="AA2">
-        <v>0.1026812738074358</v>
+        <v>0.1403067714178825</v>
       </c>
       <c r="AB2">
-        <v>0.1602898470840112</v>
+        <v>0.1351511861324736</v>
       </c>
       <c r="AC2">
-        <v>-0.05760857327657543</v>
+        <v>0.005155585285408881</v>
       </c>
       <c r="AD2">
         <v>0</v>
@@ -672,7 +672,7 @@
         <v>0</v>
       </c>
       <c r="AG2">
-        <v>-3.65</v>
+        <v>-3.51</v>
       </c>
       <c r="AH2">
         <v>0</v>
@@ -681,25 +681,25 @@
         <v>0</v>
       </c>
       <c r="AJ2">
-        <v>-0.0303030303030303</v>
+        <v>-0.02347983142685129</v>
       </c>
       <c r="AK2">
-        <v>-0.02682837192208747</v>
+        <v>-0.02379822360838022</v>
       </c>
       <c r="AL2">
         <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.418</v>
+        <v>-0.572</v>
       </c>
       <c r="AN2">
         <v>0</v>
       </c>
       <c r="AP2">
-        <v>-0.2147058823529412</v>
+        <v>-0.1553097345132743</v>
       </c>
       <c r="AQ2">
-        <v>-40.43062200956938</v>
+        <v>-39.16083916083916</v>
       </c>
     </row>
     <row r="3">
@@ -719,46 +719,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.13</v>
+        <v>0.127</v>
       </c>
       <c r="E3">
-        <v>0.0323</v>
+        <v>0.133</v>
       </c>
       <c r="G3">
-        <v>0.2551282051282051</v>
+        <v>0.2115812917594655</v>
       </c>
       <c r="H3">
-        <v>0.2551282051282051</v>
+        <v>0.2115812917594655</v>
       </c>
       <c r="I3">
-        <v>0.2166666666666666</v>
+        <v>0.2494432071269488</v>
       </c>
       <c r="J3">
-        <v>0.1763353413654619</v>
+        <v>0.2105382789371901</v>
       </c>
       <c r="K3">
-        <v>13.6</v>
+        <v>20.4</v>
       </c>
       <c r="L3">
-        <v>0.1743589743589744</v>
+        <v>0.2271714922048998</v>
       </c>
       <c r="M3">
-        <v>8.32</v>
+        <v>6.19</v>
       </c>
       <c r="N3">
-        <v>0.06704270749395649</v>
+        <v>0.04045751633986928</v>
       </c>
       <c r="O3">
-        <v>0.611764705882353</v>
+        <v>0.3034313725490196</v>
       </c>
       <c r="P3">
-        <v>8.32</v>
+        <v>6.19</v>
       </c>
       <c r="Q3">
-        <v>0.06704270749395649</v>
+        <v>0.04045751633986928</v>
       </c>
       <c r="R3">
-        <v>0.611764705882353</v>
+        <v>0.3034313725490196</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -767,31 +767,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>3.65</v>
+        <v>3.51</v>
       </c>
       <c r="V3">
-        <v>0.02941176470588235</v>
+        <v>0.02294117647058823</v>
       </c>
       <c r="W3">
-        <v>0.09742120343839542</v>
+        <v>0.1473988439306358</v>
       </c>
       <c r="X3">
-        <v>0.1602898470840112</v>
+        <v>0.1351511861324736</v>
       </c>
       <c r="Y3">
-        <v>-0.06286864364561581</v>
+        <v>0.0122476577981622</v>
       </c>
       <c r="Z3">
-        <v>0.5823068309070549</v>
+        <v>0.6664192949907235</v>
       </c>
       <c r="AA3">
-        <v>0.1026812738074358</v>
+        <v>0.1403067714178825</v>
       </c>
       <c r="AB3">
-        <v>0.1602898470840112</v>
+        <v>0.1351511861324736</v>
       </c>
       <c r="AC3">
-        <v>-0.05760857327657543</v>
+        <v>0.005155585285408881</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -803,7 +803,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-3.65</v>
+        <v>-3.51</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -812,25 +812,25 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0303030303030303</v>
+        <v>-0.02347983142685129</v>
       </c>
       <c r="AK3">
-        <v>-0.02682837192208747</v>
+        <v>-0.02379822360838022</v>
       </c>
       <c r="AL3">
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.418</v>
+        <v>-0.572</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AP3">
-        <v>-0.2147058823529412</v>
+        <v>-0.1553097345132743</v>
       </c>
       <c r="AQ3">
-        <v>-40.43062200956938</v>
+        <v>-39.16083916083916</v>
       </c>
     </row>
   </sheetData>
